--- a/BOM Format/Centroid File-JLCPCB.xlsx
+++ b/BOM Format/Centroid File-JLCPCB.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\eSpark-Hardware\BOM Format\BOM Template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\eSpark-Hardware\BOM Format\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B5298C9-D8D4-495B-A8A7-91C7CE702F74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E1C91E5-E090-4339-883B-F81E74626DB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -75,7 +75,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -90,12 +90,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="1" tint="0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -220,19 +214,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -247,6 +235,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -618,26 +612,26 @@
       <c r="E2" s="3"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
+      <c r="A4" s="5"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
     </row>
     <row r="6" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
